--- a/backup/Book_current.xlsx
+++ b/backup/Book_current.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gelsvalt-my.sharepoint.com/personal/u087_gelsva_lt/Documents/Desktop/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_7117099FE06DC4A9E9F17B7E475F4ABEEB6C74F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CB937DE-6B50-4C98-9A14-38B2A6BEA43A}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_7117099FE06DC4A9E9F17B7E475F4ABEEB6C74F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE7191CD-6609-46B0-B6F5-ABFDDD2A585A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Kods</t>
   </si>
@@ -75,9 +75,6 @@
     <t>Grostonas iela 1, Vidzemes priekšpilsēta, Rīga, LV-1013</t>
   </si>
   <si>
-    <t>Grenctāles robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907</t>
-  </si>
-  <si>
     <t>Āzenes iela 5, Kurzemes rajons</t>
   </si>
   <si>
@@ -103,24 +100,6 @@
   </si>
   <si>
     <t>Iepirkuma cena bez PVN</t>
-  </si>
-  <si>
-    <t>03V787445</t>
-  </si>
-  <si>
-    <t>Koru Bay Sauvignon Blanc Marlborough baltvīns 0,75L 13%</t>
-  </si>
-  <si>
-    <t>03MF342</t>
-  </si>
-  <si>
-    <t>4860019002091</t>
-  </si>
-  <si>
-    <t>#Borjomi gāzēts min.ūdens pet 1,25L</t>
-  </si>
-  <si>
-    <t>24.08–30.08.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Biķernieku iela 21, Vidzemes priekšpilsēta, Rīga, LV-1039
@@ -139,22 +118,46 @@
     <t>Prekės grupė</t>
   </si>
   <si>
-    <t>NON_ALC</t>
-  </si>
-  <si>
-    <t>WATER</t>
-  </si>
-  <si>
-    <t>PET_CARBO</t>
-  </si>
-  <si>
     <t>ALC</t>
   </si>
   <si>
-    <t>WINE</t>
-  </si>
-  <si>
-    <t>WHITE</t>
+    <t>69VB2702492</t>
+  </si>
+  <si>
+    <t>8028277000563</t>
+  </si>
+  <si>
+    <t>Chiara Tuncis saulespuķu eļļā 80gx3</t>
+  </si>
+  <si>
+    <t>FOOD</t>
+  </si>
+  <si>
+    <t>FISH</t>
+  </si>
+  <si>
+    <t>PRESERV</t>
+  </si>
+  <si>
+    <t>LV014399</t>
+  </si>
+  <si>
+    <t>4750142004980</t>
+  </si>
+  <si>
+    <t>#Cēsu Premium pint alus can 0,568L 5%</t>
+  </si>
+  <si>
+    <t>BEER</t>
+  </si>
+  <si>
+    <t>BOT_ALE</t>
+  </si>
+  <si>
+    <t>17.08–23.08.2026</t>
+  </si>
+  <si>
+    <t>Grenctāle, Robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907</t>
   </si>
 </sst>
 </file>
@@ -689,7 +692,7 @@
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -703,13 +706,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>3</v>
@@ -733,7 +736,7 @@
         <v>9</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>10</v>
@@ -742,151 +745,149 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="8">
-        <v>3701172716559</v>
+        <v>27</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="10">
+        <v>37</v>
+      </c>
+      <c r="H2" s="10">
+        <v>40</v>
+      </c>
+      <c r="I2" s="10">
+        <v>36</v>
+      </c>
+      <c r="J2" s="10">
+        <v>38</v>
+      </c>
+      <c r="K2" s="10">
+        <v>64</v>
+      </c>
+      <c r="L2" s="10">
+        <v>51</v>
+      </c>
+      <c r="M2" s="10">
+        <v>38</v>
+      </c>
+      <c r="N2" s="10">
+        <v>81</v>
+      </c>
+      <c r="O2" s="10">
+        <v>73</v>
+      </c>
+      <c r="P2" s="10">
         <v>23</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="10">
-        <v>8</v>
-      </c>
-      <c r="H2" s="10">
-        <v>58</v>
-      </c>
-      <c r="I2" s="10">
-        <v>64</v>
-      </c>
-      <c r="J2" s="10">
-        <v>73</v>
-      </c>
-      <c r="K2" s="10">
-        <v>105</v>
-      </c>
-      <c r="L2" s="10">
-        <v>36</v>
-      </c>
-      <c r="M2" s="10">
-        <v>46</v>
-      </c>
-      <c r="N2" s="10">
-        <v>51</v>
-      </c>
-      <c r="O2" s="10">
-        <v>26</v>
-      </c>
-      <c r="P2" s="10">
-        <v>49</v>
-      </c>
       <c r="Q2" s="10">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="R2" s="10">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="S2" s="10">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="T2" s="10">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="U2" s="11">
-        <f>SUM(G2:T2)</f>
-        <v>642</v>
+        <v>709</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>38</v>
-      </c>
       <c r="G3" s="10">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="H3" s="10">
-        <v>49</v>
+        <v>315</v>
       </c>
       <c r="I3" s="10">
-        <v>69</v>
+        <v>223</v>
       </c>
       <c r="J3" s="10">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K3" s="10">
-        <v>98</v>
+        <v>351</v>
       </c>
       <c r="L3" s="10">
-        <v>105</v>
+        <v>1079</v>
       </c>
       <c r="M3" s="10">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="N3" s="10">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="O3" s="10">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="P3" s="10">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="Q3" s="10">
-        <v>71</v>
+        <v>357</v>
       </c>
       <c r="R3" s="10">
-        <v>76</v>
+        <v>221</v>
       </c>
       <c r="S3" s="10">
-        <v>62</v>
+        <v>678</v>
       </c>
       <c r="T3" s="10">
-        <v>46</v>
+        <v>382</v>
       </c>
       <c r="U3" s="11">
-        <f>SUM(G3:T3)</f>
-        <v>924</v>
+        <v>4541</v>
       </c>
     </row>
   </sheetData>
@@ -912,52 +913,52 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>17</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>23</v>
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="B5" s="13">
-        <v>4.79</v>
+        <v>2</v>
       </c>
       <c r="C5" s="13">
-        <v>3.0281000000000002</v>
+        <v>1.66</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B6" s="13">
-        <v>1.85</v>
+        <v>0.89</v>
       </c>
       <c r="C6" s="13">
-        <v>1.43</v>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>

--- a/backup/Book_current.xlsx
+++ b/backup/Book_current.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gelsvalt-my.sharepoint.com/personal/u087_gelsva_lt/Documents/Desktop/python/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_7117099FE06DC4A9E9F17B7E475F4ABEEB6C74F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE7191CD-6609-46B0-B6F5-ABFDDD2A585A}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_7117099FE06DC4A9E9F17B7E475F4ABEEB6C74F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5066776A-8C5B-4FF8-8A67-0101348DA11B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,13 +121,7 @@
     <t>ALC</t>
   </si>
   <si>
-    <t>69VB2702492</t>
-  </si>
-  <si>
-    <t>8028277000563</t>
-  </si>
-  <si>
-    <t>Chiara Tuncis saulespuķu eļļā 80gx3</t>
+    <t>Grenctāle, Robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907</t>
   </si>
   <si>
     <t>FOOD</t>
@@ -139,25 +133,31 @@
     <t>PRESERV</t>
   </si>
   <si>
-    <t>LV014399</t>
-  </si>
-  <si>
-    <t>4750142004980</t>
-  </si>
-  <si>
-    <t>#Cēsu Premium pint alus can 0,568L 5%</t>
-  </si>
-  <si>
     <t>BEER</t>
   </si>
   <si>
     <t>BOT_ALE</t>
   </si>
   <si>
-    <t>17.08–23.08.2026</t>
-  </si>
-  <si>
-    <t>Grenctāle, Robežkontroles punkts, Brunavas pagasts, Bauskas novads, LV-3907</t>
+    <t>31.08–06.09.2026</t>
+  </si>
+  <si>
+    <t>CH1000645</t>
+  </si>
+  <si>
+    <t>9002859051753</t>
+  </si>
+  <si>
+    <t>Sardīnes saulespuķu eļļā 115g</t>
+  </si>
+  <si>
+    <t>LV014398</t>
+  </si>
+  <si>
+    <t>4750142005062</t>
+  </si>
+  <si>
+    <t>#Cēsu Brūža nefiltrets alus can 0,568L 5,4%</t>
   </si>
 </sst>
 </file>
@@ -235,6 +235,7 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -745,7 +746,7 @@
         <v>11</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>12</v>
@@ -762,132 +763,134 @@
     </row>
     <row r="2" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>32</v>
-      </c>
       <c r="G2" s="10">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="H2" s="10">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="I2" s="10">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="J2" s="10">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K2" s="10">
-        <v>64</v>
+        <v>208</v>
       </c>
       <c r="L2" s="10">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="M2" s="10">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="N2" s="10">
-        <v>81</v>
+        <v>161</v>
       </c>
       <c r="O2" s="10">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P2" s="10">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="Q2" s="10">
-        <v>30</v>
+        <v>169</v>
       </c>
       <c r="R2" s="10">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="S2" s="10">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="T2" s="10">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="U2" s="11">
-        <v>709</v>
+        <f>SUM(G2:T2)</f>
+        <v>1633</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G3" s="10">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="H3" s="10">
-        <v>315</v>
+        <v>76</v>
       </c>
       <c r="I3" s="10">
-        <v>223</v>
+        <v>110</v>
       </c>
       <c r="J3" s="10">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="K3" s="10">
-        <v>351</v>
+        <v>162</v>
       </c>
       <c r="L3" s="10">
-        <v>1079</v>
+        <v>352</v>
       </c>
       <c r="M3" s="10">
-        <v>197</v>
+        <v>102</v>
       </c>
       <c r="N3" s="10">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="O3" s="10">
-        <v>223</v>
+        <v>138</v>
       </c>
       <c r="P3" s="10">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="Q3" s="10">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="R3" s="10">
-        <v>221</v>
+        <v>84</v>
       </c>
       <c r="S3" s="10">
-        <v>678</v>
+        <v>319</v>
       </c>
       <c r="T3" s="10">
-        <v>382</v>
+        <v>158</v>
       </c>
       <c r="U3" s="11">
-        <v>4541</v>
+        <f>SUM(G3:T3)</f>
+        <v>2089</v>
       </c>
     </row>
   </sheetData>
@@ -925,7 +928,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -939,29 +942,30 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>29</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>36</v>
       </c>
       <c r="B5" s="13">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="C5" s="13">
-        <v>1.66</v>
+        <v>0.91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>35</v>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>39</v>
       </c>
       <c r="B6" s="13">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="C6" s="13">
-        <v>0.72</v>
+        <v>0.86392000000000002</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>